--- a/Estado_Da_Nacao_2026.xlsx
+++ b/Estado_Da_Nacao_2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c241d2b43e4dbbd9/Ambiente de Trabalho/PhD/FlowDisco/FlowDisco/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c241d2b43e4dbbd9/Ambiente de Trabalho/PhD/Conferencias/PROPOR26_LongPaper/dados_parlamento/estado_nacao/Estado_da_Nacao_2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="628" documentId="11_0AB9D3BCD36051661FD82D11595ED87656DE161C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82996CC2-D9E6-44B2-8E06-90166B98F81F}"/>
+  <xr:revisionPtr revIDLastSave="501" documentId="11_0AB9D3BCD36051661FD82D11595ED87656DE161C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F24345FC-29AA-4BC7-856F-6B515876B221}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4177,6 +4177,9 @@
     <t>… deixar-lhe o seguinte conselho: o Sr. Deputado André Ventura, que diz que quer ser Primeiro-Ministro, antes de querer vir para a piscina dos grandes, aprenda com quem já aprendeu a nadar.</t>
   </si>
   <si>
+    <t>Continuação dos protestos do CH.</t>
+  </si>
+  <si>
     <t>Aprenda com quem já aprendeu a nadar, porque o País não é o caos, o País não é berraria, o País são as soluções e é isso que nós queremos!</t>
   </si>
   <si>
@@ -4709,9 +4712,6 @@
   </si>
   <si>
     <t>Passamos ao encerramento do debate e, para o efeito, tem a palavra o Sr. Ministro da Economia e da Coesão Territorial.</t>
-  </si>
-  <si>
-    <t>açãp</t>
   </si>
   <si>
     <t>Srs. Deputados, vamos criar condições para o Sr. Ministro encerrar o debate.</t>
@@ -4931,10 +4931,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5225,10 +5221,13 @@
   <dimension ref="A1:J2038"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="22.453125" customWidth="1"/>
     <col min="4" max="4" width="21.6328125" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="105.81640625" customWidth="1"/>
+    <col min="6" max="6" width="73.36328125" customWidth="1"/>
     <col min="7" max="7" width="12.26953125" customWidth="1"/>
+    <col min="9" max="9" width="16.7265625" customWidth="1"/>
+    <col min="10" max="10" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -6424,7 +6423,7 @@
         <v>13</v>
       </c>
       <c r="J46" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.35">
@@ -6554,7 +6553,7 @@
         <v>13</v>
       </c>
       <c r="J51" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.35">
@@ -7308,7 +7307,7 @@
         <v>13</v>
       </c>
       <c r="J80" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.35">
@@ -8478,7 +8477,7 @@
         <v>13</v>
       </c>
       <c r="J125" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.35">
@@ -8686,7 +8685,7 @@
         <v>13</v>
       </c>
       <c r="J133" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.35">
@@ -10038,7 +10037,7 @@
         <v>13</v>
       </c>
       <c r="J185" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.35">
@@ -10090,7 +10089,7 @@
         <v>13</v>
       </c>
       <c r="J187" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.35">
@@ -11338,7 +11337,7 @@
         <v>13</v>
       </c>
       <c r="J235" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.35">
@@ -11806,7 +11805,7 @@
         <v>13</v>
       </c>
       <c r="J253" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.35">
@@ -11988,7 +11987,7 @@
         <v>13</v>
       </c>
       <c r="J260" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.35">
@@ -13834,7 +13833,7 @@
         <v>13</v>
       </c>
       <c r="J331" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.35">
@@ -16590,7 +16589,7 @@
         <v>13</v>
       </c>
       <c r="J437" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="438" spans="1:10" x14ac:dyDescent="0.35">
@@ -17396,7 +17395,7 @@
         <v>13</v>
       </c>
       <c r="J468" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="469" spans="1:10" x14ac:dyDescent="0.35">
@@ -18410,7 +18409,7 @@
         <v>13</v>
       </c>
       <c r="J507" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="508" spans="1:10" x14ac:dyDescent="0.35">
@@ -18462,7 +18461,7 @@
         <v>13</v>
       </c>
       <c r="J509" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="510" spans="1:10" x14ac:dyDescent="0.35">
@@ -19502,7 +19501,7 @@
         <v>13</v>
       </c>
       <c r="J549" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="550" spans="1:10" x14ac:dyDescent="0.35">
@@ -19606,7 +19605,7 @@
         <v>13</v>
       </c>
       <c r="J553" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="554" spans="1:10" x14ac:dyDescent="0.35">
@@ -19658,7 +19657,7 @@
         <v>13</v>
       </c>
       <c r="J555" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="556" spans="1:10" x14ac:dyDescent="0.35">
@@ -20100,7 +20099,7 @@
         <v>13</v>
       </c>
       <c r="J572" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="573" spans="1:10" x14ac:dyDescent="0.35">
@@ -20308,7 +20307,7 @@
         <v>13</v>
       </c>
       <c r="J580" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="581" spans="1:10" x14ac:dyDescent="0.35">
@@ -22518,7 +22517,7 @@
         <v>13</v>
       </c>
       <c r="J665" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="666" spans="1:10" x14ac:dyDescent="0.35">
@@ -22778,7 +22777,7 @@
         <v>13</v>
       </c>
       <c r="J675" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="676" spans="1:10" x14ac:dyDescent="0.35">
@@ -22908,7 +22907,7 @@
         <v>13</v>
       </c>
       <c r="J680" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="681" spans="1:10" x14ac:dyDescent="0.35">
@@ -24052,7 +24051,7 @@
         <v>13</v>
       </c>
       <c r="J724" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="725" spans="1:10" x14ac:dyDescent="0.35">
@@ -24598,7 +24597,7 @@
         <v>13</v>
       </c>
       <c r="J745" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="746" spans="1:10" x14ac:dyDescent="0.35">
@@ -24754,7 +24753,7 @@
         <v>13</v>
       </c>
       <c r="J751" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="752" spans="1:10" x14ac:dyDescent="0.35">
@@ -25144,7 +25143,7 @@
         <v>13</v>
       </c>
       <c r="J766" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="767" spans="1:10" x14ac:dyDescent="0.35">
@@ -25788,7 +25787,7 @@
         <v>13</v>
       </c>
       <c r="J791" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="792" spans="1:10" x14ac:dyDescent="0.35">
@@ -26256,7 +26255,7 @@
         <v>13</v>
       </c>
       <c r="J809" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="810" spans="1:10" x14ac:dyDescent="0.35">
@@ -26412,7 +26411,7 @@
         <v>13</v>
       </c>
       <c r="J815" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="816" spans="1:10" x14ac:dyDescent="0.35">
@@ -26802,7 +26801,7 @@
         <v>13</v>
       </c>
       <c r="J830" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="831" spans="1:10" x14ac:dyDescent="0.35">
@@ -27452,7 +27451,7 @@
         <v>13</v>
       </c>
       <c r="J855" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="856" spans="1:10" x14ac:dyDescent="0.35">
@@ -27478,7 +27477,7 @@
         <v>13</v>
       </c>
       <c r="J856" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="857" spans="1:10" x14ac:dyDescent="0.35">
@@ -27816,7 +27815,7 @@
         <v>13</v>
       </c>
       <c r="J869" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="870" spans="1:10" x14ac:dyDescent="0.35">
@@ -28726,7 +28725,7 @@
         <v>13</v>
       </c>
       <c r="J904" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="905" spans="1:10" x14ac:dyDescent="0.35">
@@ -29272,7 +29271,7 @@
         <v>13</v>
       </c>
       <c r="J925" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="926" spans="1:10" x14ac:dyDescent="0.35">
@@ -29818,7 +29817,7 @@
         <v>13</v>
       </c>
       <c r="J946" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="947" spans="1:10" x14ac:dyDescent="0.35">
@@ -29844,7 +29843,7 @@
         <v>13</v>
       </c>
       <c r="J947" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="948" spans="1:10" x14ac:dyDescent="0.35">
@@ -30806,7 +30805,7 @@
         <v>13</v>
       </c>
       <c r="J984" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="985" spans="1:10" x14ac:dyDescent="0.35">
@@ -31274,7 +31273,7 @@
         <v>13</v>
       </c>
       <c r="J1002" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1003" spans="1:10" x14ac:dyDescent="0.35">
@@ -32236,7 +32235,7 @@
         <v>13</v>
       </c>
       <c r="J1039" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1040" spans="1:10" x14ac:dyDescent="0.35">
@@ -33250,7 +33249,7 @@
         <v>13</v>
       </c>
       <c r="J1078" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1079" spans="1:10" x14ac:dyDescent="0.35">
@@ -33562,7 +33561,7 @@
         <v>13</v>
       </c>
       <c r="J1090" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1091" spans="1:10" x14ac:dyDescent="0.35">
@@ -34264,7 +34263,7 @@
         <v>13</v>
       </c>
       <c r="J1117" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1118" spans="1:10" x14ac:dyDescent="0.35">
@@ -34290,7 +34289,7 @@
         <v>13</v>
       </c>
       <c r="J1118" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1119" spans="1:10" x14ac:dyDescent="0.35">
@@ -34420,7 +34419,7 @@
         <v>13</v>
       </c>
       <c r="J1123" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1124" spans="1:10" x14ac:dyDescent="0.35">
@@ -34680,7 +34679,7 @@
         <v>13</v>
       </c>
       <c r="J1133" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1134" spans="1:10" x14ac:dyDescent="0.35">
@@ -34940,7 +34939,7 @@
         <v>13</v>
       </c>
       <c r="J1143" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1144" spans="1:10" x14ac:dyDescent="0.35">
@@ -34966,7 +34965,7 @@
         <v>13</v>
       </c>
       <c r="J1144" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1145" spans="1:10" x14ac:dyDescent="0.35">
@@ -35018,7 +35017,7 @@
         <v>13</v>
       </c>
       <c r="J1146" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1147" spans="1:10" x14ac:dyDescent="0.35">
@@ -35434,7 +35433,7 @@
         <v>13</v>
       </c>
       <c r="J1162" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1163" spans="1:10" x14ac:dyDescent="0.35">
@@ -35720,7 +35719,7 @@
         <v>13</v>
       </c>
       <c r="J1173" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1174" spans="1:10" x14ac:dyDescent="0.35">
@@ -35902,7 +35901,7 @@
         <v>13</v>
       </c>
       <c r="J1180" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1181" spans="1:10" x14ac:dyDescent="0.35">
@@ -35928,7 +35927,7 @@
         <v>13</v>
       </c>
       <c r="J1181" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1182" spans="1:10" x14ac:dyDescent="0.35">
@@ -35980,7 +35979,7 @@
         <v>13</v>
       </c>
       <c r="J1183" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1184" spans="1:10" x14ac:dyDescent="0.35">
@@ -36760,7 +36759,7 @@
         <v>13</v>
       </c>
       <c r="J1213" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1214" spans="1:10" x14ac:dyDescent="0.35">
@@ -37176,7 +37175,7 @@
         <v>13</v>
       </c>
       <c r="J1229" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1230" spans="1:10" x14ac:dyDescent="0.35">
@@ -37410,7 +37409,7 @@
         <v>13</v>
       </c>
       <c r="J1238" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1239" spans="1:10" x14ac:dyDescent="0.35">
@@ -37488,7 +37487,7 @@
         <v>13</v>
       </c>
       <c r="J1241" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1242" spans="1:10" x14ac:dyDescent="0.35">
@@ -37514,7 +37513,7 @@
         <v>13</v>
       </c>
       <c r="J1242" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1243" spans="1:10" x14ac:dyDescent="0.35">
@@ -38086,7 +38085,7 @@
         <v>13</v>
       </c>
       <c r="J1264" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1265" spans="1:10" x14ac:dyDescent="0.35">
@@ -38112,7 +38111,7 @@
         <v>13</v>
       </c>
       <c r="J1265" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1266" spans="1:10" x14ac:dyDescent="0.35">
@@ -38294,7 +38293,7 @@
         <v>13</v>
       </c>
       <c r="J1272" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1273" spans="1:10" x14ac:dyDescent="0.35">
@@ -38840,7 +38839,7 @@
         <v>13</v>
       </c>
       <c r="J1293" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1294" spans="1:10" x14ac:dyDescent="0.35">
@@ -38892,7 +38891,7 @@
         <v>13</v>
       </c>
       <c r="J1295" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1296" spans="1:10" x14ac:dyDescent="0.35">
@@ -39542,7 +39541,7 @@
         <v>13</v>
       </c>
       <c r="J1320" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1321" spans="1:10" x14ac:dyDescent="0.35">
@@ -39620,7 +39619,7 @@
         <v>13</v>
       </c>
       <c r="J1323" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1324" spans="1:10" x14ac:dyDescent="0.35">
@@ -39646,7 +39645,7 @@
         <v>13</v>
       </c>
       <c r="J1324" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1325" spans="1:10" x14ac:dyDescent="0.35">
@@ -39724,7 +39723,7 @@
         <v>13</v>
       </c>
       <c r="J1327" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1328" spans="1:10" x14ac:dyDescent="0.35">
@@ -39776,7 +39775,7 @@
         <v>13</v>
       </c>
       <c r="J1329" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1330" spans="1:10" x14ac:dyDescent="0.35">
@@ -40960,7 +40959,7 @@
         <v>13</v>
       </c>
       <c r="J1375" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1376" spans="1:10" x14ac:dyDescent="0.35">
@@ -41500,7 +41499,7 @@
         <v>13</v>
       </c>
       <c r="J1396" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1397" spans="1:10" x14ac:dyDescent="0.35">
@@ -41552,7 +41551,7 @@
         <v>13</v>
       </c>
       <c r="J1398" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1399" spans="1:10" x14ac:dyDescent="0.35">
@@ -41656,7 +41655,7 @@
         <v>13</v>
       </c>
       <c r="J1402" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1403" spans="1:10" x14ac:dyDescent="0.35">
@@ -41708,7 +41707,7 @@
         <v>13</v>
       </c>
       <c r="J1404" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1405" spans="1:10" x14ac:dyDescent="0.35">
@@ -41760,7 +41759,7 @@
         <v>13</v>
       </c>
       <c r="J1406" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1407" spans="1:10" x14ac:dyDescent="0.35">
@@ -41786,7 +41785,7 @@
         <v>13</v>
       </c>
       <c r="J1407" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1408" spans="1:10" x14ac:dyDescent="0.35">
@@ -41812,7 +41811,7 @@
         <v>13</v>
       </c>
       <c r="J1408" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1409" spans="1:10" x14ac:dyDescent="0.35">
@@ -41838,7 +41837,7 @@
         <v>13</v>
       </c>
       <c r="J1409" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1410" spans="1:10" x14ac:dyDescent="0.35">
@@ -42332,7 +42331,7 @@
         <v>13</v>
       </c>
       <c r="J1428" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1429" spans="1:10" x14ac:dyDescent="0.35">
@@ -43990,7 +43989,7 @@
         <v>13</v>
       </c>
       <c r="J1492" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1493" spans="1:10" x14ac:dyDescent="0.35">
@@ -44042,7 +44041,7 @@
         <v>13</v>
       </c>
       <c r="J1494" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1495" spans="1:10" x14ac:dyDescent="0.35">
@@ -44068,7 +44067,7 @@
         <v>13</v>
       </c>
       <c r="J1495" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1496" spans="1:10" x14ac:dyDescent="0.35">
@@ -44726,7 +44725,7 @@
         <v>13</v>
       </c>
       <c r="J1521" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1522" spans="1:10" x14ac:dyDescent="0.35">
@@ -45572,7 +45571,7 @@
         <v>13</v>
       </c>
       <c r="J1554" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1555" spans="1:10" x14ac:dyDescent="0.35">
@@ -46300,7 +46299,7 @@
         <v>13</v>
       </c>
       <c r="J1582" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1583" spans="1:10" x14ac:dyDescent="0.35">
@@ -46502,7 +46501,7 @@
         <v>13</v>
       </c>
       <c r="J1590" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1591" spans="1:10" x14ac:dyDescent="0.35">
@@ -46658,7 +46657,7 @@
         <v>13</v>
       </c>
       <c r="J1596" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1597" spans="1:10" x14ac:dyDescent="0.35">
@@ -47718,7 +47717,7 @@
         <v>13</v>
       </c>
       <c r="J1637" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1638" spans="1:10" x14ac:dyDescent="0.35">
@@ -48004,7 +48003,7 @@
         <v>13</v>
       </c>
       <c r="J1648" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1649" spans="1:10" x14ac:dyDescent="0.35">
@@ -48596,7 +48595,7 @@
         <v>13</v>
       </c>
       <c r="J1671" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1672" spans="1:10" x14ac:dyDescent="0.35">
@@ -48934,7 +48933,7 @@
         <v>13</v>
       </c>
       <c r="J1684" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1685" spans="1:10" x14ac:dyDescent="0.35">
@@ -50364,7 +50363,7 @@
         <v>13</v>
       </c>
       <c r="J1739" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1740" spans="1:10" x14ac:dyDescent="0.35">
@@ -50742,19 +50741,19 @@
         <v>138</v>
       </c>
       <c r="D1754" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="E1754" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1754" t="s">
-        <v>1369</v>
+        <v>31</v>
+      </c>
+      <c r="F1754" t="s">
+        <v>1385</v>
       </c>
       <c r="H1754" t="s">
-        <v>17</v>
-      </c>
-      <c r="I1754" t="s">
-        <v>60</v>
+        <v>13</v>
+      </c>
+      <c r="J1754" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="1755" spans="1:10" x14ac:dyDescent="0.35">
@@ -50774,7 +50773,7 @@
         <v>31</v>
       </c>
       <c r="F1755" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="H1755" t="s">
         <v>13</v>
@@ -50800,7 +50799,7 @@
         <v>31</v>
       </c>
       <c r="G1756" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="H1756" t="s">
         <v>17</v>
@@ -50826,7 +50825,7 @@
         <v>37</v>
       </c>
       <c r="G1757" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="H1757" t="s">
         <v>17</v>
@@ -50852,7 +50851,7 @@
         <v>69</v>
       </c>
       <c r="G1758" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="H1758" t="s">
         <v>17</v>
@@ -50878,7 +50877,7 @@
         <v>31</v>
       </c>
       <c r="F1759" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="H1759" t="s">
         <v>13</v>
@@ -50904,7 +50903,7 @@
         <v>767</v>
       </c>
       <c r="F1760" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="H1760" t="s">
         <v>13</v>
@@ -50930,7 +50929,7 @@
         <v>767</v>
       </c>
       <c r="F1761" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="H1761" t="s">
         <v>13</v>
@@ -50956,7 +50955,7 @@
         <v>69</v>
       </c>
       <c r="F1762" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="H1762" t="s">
         <v>13</v>
@@ -50982,7 +50981,7 @@
         <v>69</v>
       </c>
       <c r="F1763" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="H1763" t="s">
         <v>13</v>
@@ -51034,7 +51033,7 @@
         <v>69</v>
       </c>
       <c r="G1765" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="H1765" t="s">
         <v>17</v>
@@ -51060,7 +51059,7 @@
         <v>69</v>
       </c>
       <c r="F1766" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="H1766" t="s">
         <v>13</v>
@@ -51112,7 +51111,7 @@
         <v>69</v>
       </c>
       <c r="G1768" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="H1768" t="s">
         <v>17</v>
@@ -51138,7 +51137,7 @@
         <v>69</v>
       </c>
       <c r="F1769" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="H1769" t="s">
         <v>13</v>
@@ -51164,7 +51163,7 @@
         <v>69</v>
       </c>
       <c r="F1770" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="H1770" t="s">
         <v>13</v>
@@ -51190,7 +51189,7 @@
         <v>31</v>
       </c>
       <c r="F1771" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="H1771" t="s">
         <v>13</v>
@@ -51216,7 +51215,7 @@
         <v>69</v>
       </c>
       <c r="F1772" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="H1772" t="s">
         <v>13</v>
@@ -51242,7 +51241,7 @@
         <v>69</v>
       </c>
       <c r="G1773" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="H1773" t="s">
         <v>17</v>
@@ -51268,13 +51267,13 @@
         <v>69</v>
       </c>
       <c r="F1774" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="H1774" t="s">
         <v>13</v>
       </c>
       <c r="J1774" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1775" spans="1:10" x14ac:dyDescent="0.35">
@@ -51300,7 +51299,7 @@
         <v>13</v>
       </c>
       <c r="J1775" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1776" spans="1:10" x14ac:dyDescent="0.35">
@@ -51326,7 +51325,7 @@
         <v>13</v>
       </c>
       <c r="J1776" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1777" spans="1:10" x14ac:dyDescent="0.35">
@@ -51346,7 +51345,7 @@
         <v>69</v>
       </c>
       <c r="F1777" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="H1777" t="s">
         <v>13</v>
@@ -51372,7 +51371,7 @@
         <v>69</v>
       </c>
       <c r="F1778" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="H1778" t="s">
         <v>13</v>
@@ -51398,7 +51397,7 @@
         <v>69</v>
       </c>
       <c r="F1779" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="H1779" t="s">
         <v>13</v>
@@ -51450,7 +51449,7 @@
         <v>69</v>
       </c>
       <c r="F1781" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="H1781" t="s">
         <v>13</v>
@@ -51476,7 +51475,7 @@
         <v>69</v>
       </c>
       <c r="F1782" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="H1782" t="s">
         <v>13</v>
@@ -51502,7 +51501,7 @@
         <v>69</v>
       </c>
       <c r="F1783" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="H1783" t="s">
         <v>13</v>
@@ -51528,7 +51527,7 @@
         <v>69</v>
       </c>
       <c r="F1784" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="H1784" t="s">
         <v>13</v>
@@ -51554,7 +51553,7 @@
         <v>31</v>
       </c>
       <c r="G1785" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="H1785" t="s">
         <v>17</v>
@@ -51605,14 +51604,14 @@
       <c r="E1787" t="s">
         <v>69</v>
       </c>
-      <c r="G1787" t="s">
-        <v>1410</v>
+      <c r="F1787" t="s">
+        <v>1411</v>
       </c>
       <c r="H1787" t="s">
-        <v>17</v>
-      </c>
-      <c r="I1787" t="s">
-        <v>18</v>
+        <v>13</v>
+      </c>
+      <c r="J1787" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="1788" spans="1:10" x14ac:dyDescent="0.35">
@@ -51632,7 +51631,7 @@
         <v>69</v>
       </c>
       <c r="F1788" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="H1788" t="s">
         <v>13</v>
@@ -51658,13 +51657,13 @@
         <v>69</v>
       </c>
       <c r="F1789" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="H1789" t="s">
         <v>13</v>
       </c>
       <c r="J1789" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1790" spans="1:10" x14ac:dyDescent="0.35">
@@ -51684,7 +51683,7 @@
         <v>767</v>
       </c>
       <c r="F1790" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="H1790" t="s">
         <v>13</v>
@@ -51710,7 +51709,7 @@
         <v>69</v>
       </c>
       <c r="F1791" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="H1791" t="s">
         <v>13</v>
@@ -51736,7 +51735,7 @@
         <v>767</v>
       </c>
       <c r="F1792" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="H1792" t="s">
         <v>13</v>
@@ -51762,7 +51761,7 @@
         <v>69</v>
       </c>
       <c r="F1793" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="H1793" t="s">
         <v>13</v>
@@ -51788,7 +51787,7 @@
         <v>767</v>
       </c>
       <c r="F1794" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="H1794" t="s">
         <v>13</v>
@@ -51814,7 +51813,7 @@
         <v>767</v>
       </c>
       <c r="F1795" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="H1795" t="s">
         <v>13</v>
@@ -51840,7 +51839,7 @@
         <v>69</v>
       </c>
       <c r="F1796" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="H1796" t="s">
         <v>13</v>
@@ -51866,7 +51865,7 @@
         <v>69</v>
       </c>
       <c r="F1797" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="H1797" t="s">
         <v>13</v>
@@ -51892,7 +51891,7 @@
         <v>69</v>
       </c>
       <c r="F1798" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="H1798" t="s">
         <v>13</v>
@@ -51918,13 +51917,13 @@
         <v>69</v>
       </c>
       <c r="F1799" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="H1799" t="s">
         <v>13</v>
       </c>
       <c r="J1799" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1800" spans="1:10" x14ac:dyDescent="0.35">
@@ -51944,7 +51943,7 @@
         <v>69</v>
       </c>
       <c r="F1800" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="H1800" t="s">
         <v>13</v>
@@ -51970,7 +51969,7 @@
         <v>69</v>
       </c>
       <c r="F1801" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="H1801" t="s">
         <v>13</v>
@@ -51996,13 +51995,13 @@
         <v>31</v>
       </c>
       <c r="F1802" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="H1802" t="s">
         <v>13</v>
       </c>
       <c r="J1802" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1803" spans="1:10" x14ac:dyDescent="0.35">
@@ -52022,13 +52021,13 @@
         <v>69</v>
       </c>
       <c r="F1803" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="H1803" t="s">
         <v>13</v>
       </c>
       <c r="J1803" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1804" spans="1:10" x14ac:dyDescent="0.35">
@@ -52048,7 +52047,7 @@
         <v>31</v>
       </c>
       <c r="F1804" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="H1804" t="s">
         <v>13</v>
@@ -52074,7 +52073,7 @@
         <v>69</v>
       </c>
       <c r="F1805" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="H1805" t="s">
         <v>13</v>
@@ -52100,7 +52099,7 @@
         <v>69</v>
       </c>
       <c r="F1806" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="H1806" t="s">
         <v>13</v>
@@ -52152,7 +52151,7 @@
         <v>69</v>
       </c>
       <c r="F1808" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="H1808" t="s">
         <v>13</v>
@@ -52204,7 +52203,7 @@
         <v>69</v>
       </c>
       <c r="F1810" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="H1810" t="s">
         <v>13</v>
@@ -52256,7 +52255,7 @@
         <v>69</v>
       </c>
       <c r="F1812" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="H1812" t="s">
         <v>13</v>
@@ -52282,13 +52281,13 @@
         <v>31</v>
       </c>
       <c r="F1813" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="H1813" t="s">
         <v>13</v>
       </c>
       <c r="J1813" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1814" spans="1:10" x14ac:dyDescent="0.35">
@@ -52308,7 +52307,7 @@
         <v>69</v>
       </c>
       <c r="F1814" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="H1814" t="s">
         <v>13</v>
@@ -52386,7 +52385,7 @@
         <v>69</v>
       </c>
       <c r="F1817" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="H1817" t="s">
         <v>13</v>
@@ -52464,7 +52463,7 @@
         <v>767</v>
       </c>
       <c r="F1820" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="H1820" t="s">
         <v>13</v>
@@ -52490,7 +52489,7 @@
         <v>767</v>
       </c>
       <c r="F1821" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="H1821" t="s">
         <v>13</v>
@@ -52516,7 +52515,7 @@
         <v>767</v>
       </c>
       <c r="F1822" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="H1822" t="s">
         <v>13</v>
@@ -52588,7 +52587,7 @@
         <v>767</v>
       </c>
       <c r="F1825" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="H1825" t="s">
         <v>13</v>
@@ -52614,7 +52613,7 @@
         <v>767</v>
       </c>
       <c r="F1826" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="H1826" t="s">
         <v>13</v>
@@ -52640,7 +52639,7 @@
         <v>767</v>
       </c>
       <c r="F1827" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="H1827" t="s">
         <v>13</v>
@@ -52744,7 +52743,7 @@
         <v>52</v>
       </c>
       <c r="F1831" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="H1831" t="s">
         <v>13</v>
@@ -52770,7 +52769,7 @@
         <v>52</v>
       </c>
       <c r="F1832" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="H1832" t="s">
         <v>13</v>
@@ -52822,7 +52821,7 @@
         <v>52</v>
       </c>
       <c r="G1834" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="H1834" t="s">
         <v>17</v>
@@ -52874,7 +52873,7 @@
         <v>52</v>
       </c>
       <c r="G1836" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="H1836" t="s">
         <v>17</v>
@@ -52900,7 +52899,7 @@
         <v>52</v>
       </c>
       <c r="F1837" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="H1837" t="s">
         <v>13</v>
@@ -52920,19 +52919,19 @@
         <v>222</v>
       </c>
       <c r="D1838" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="E1838" t="s">
         <v>31</v>
       </c>
       <c r="F1838" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="H1838" t="s">
         <v>13</v>
       </c>
       <c r="J1838" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1839" spans="1:10" x14ac:dyDescent="0.35">
@@ -52978,7 +52977,7 @@
         <v>52</v>
       </c>
       <c r="G1840" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="H1840" t="s">
         <v>17</v>
@@ -53004,13 +53003,13 @@
         <v>52</v>
       </c>
       <c r="F1841" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="H1841" t="s">
         <v>13</v>
       </c>
       <c r="J1841" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1842" spans="1:10" x14ac:dyDescent="0.35">
@@ -53056,7 +53055,7 @@
         <v>52</v>
       </c>
       <c r="F1843" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="H1843" t="s">
         <v>13</v>
@@ -53082,7 +53081,7 @@
         <v>52</v>
       </c>
       <c r="F1844" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="H1844" t="s">
         <v>13</v>
@@ -53108,7 +53107,7 @@
         <v>52</v>
       </c>
       <c r="F1845" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="H1845" t="s">
         <v>13</v>
@@ -53134,7 +53133,7 @@
         <v>52</v>
       </c>
       <c r="F1846" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="H1846" t="s">
         <v>13</v>
@@ -53160,7 +53159,7 @@
         <v>52</v>
       </c>
       <c r="G1847" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="H1847" t="s">
         <v>17</v>
@@ -53186,7 +53185,7 @@
         <v>52</v>
       </c>
       <c r="F1848" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="H1848" t="s">
         <v>13</v>
@@ -53238,7 +53237,7 @@
         <v>52</v>
       </c>
       <c r="F1850" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="H1850" t="s">
         <v>13</v>
@@ -53290,7 +53289,7 @@
         <v>52</v>
       </c>
       <c r="F1852" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="H1852" t="s">
         <v>13</v>
@@ -53368,7 +53367,7 @@
         <v>52</v>
       </c>
       <c r="F1855" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="H1855" t="s">
         <v>13</v>
@@ -53388,7 +53387,7 @@
         <v>240</v>
       </c>
       <c r="D1856" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="E1856" t="s">
         <v>52</v>
@@ -53420,7 +53419,7 @@
         <v>52</v>
       </c>
       <c r="F1857" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="H1857" t="s">
         <v>13</v>
@@ -53446,7 +53445,7 @@
         <v>52</v>
       </c>
       <c r="F1858" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="H1858" t="s">
         <v>13</v>
@@ -53472,7 +53471,7 @@
         <v>52</v>
       </c>
       <c r="G1859" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="H1859" t="s">
         <v>17</v>
@@ -53498,7 +53497,7 @@
         <v>31</v>
       </c>
       <c r="G1860" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="H1860" t="s">
         <v>17</v>
@@ -53524,7 +53523,7 @@
         <v>69</v>
       </c>
       <c r="G1861" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="H1861" t="s">
         <v>17</v>
@@ -53550,7 +53549,7 @@
         <v>767</v>
       </c>
       <c r="F1862" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="H1862" t="s">
         <v>13</v>
@@ -53576,7 +53575,7 @@
         <v>767</v>
       </c>
       <c r="F1863" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="H1863" t="s">
         <v>13</v>
@@ -53622,13 +53621,13 @@
         <v>249</v>
       </c>
       <c r="D1865" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="E1865" t="s">
         <v>31</v>
       </c>
       <c r="F1865" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="H1865" t="s">
         <v>13</v>
@@ -53648,13 +53647,13 @@
         <v>250</v>
       </c>
       <c r="D1866" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="E1866" t="s">
         <v>31</v>
       </c>
       <c r="F1866" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="H1866" t="s">
         <v>13</v>
@@ -53674,7 +53673,7 @@
         <v>251</v>
       </c>
       <c r="D1867" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="E1867" t="s">
         <v>31</v>
@@ -53700,13 +53699,13 @@
         <v>252</v>
       </c>
       <c r="D1868" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="E1868" t="s">
         <v>31</v>
       </c>
       <c r="F1868" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="H1868" t="s">
         <v>13</v>
@@ -53726,13 +53725,13 @@
         <v>253</v>
       </c>
       <c r="D1869" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="E1869" t="s">
         <v>31</v>
       </c>
       <c r="F1869" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="H1869" t="s">
         <v>13</v>
@@ -53752,13 +53751,13 @@
         <v>254</v>
       </c>
       <c r="D1870" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="E1870" t="s">
         <v>31</v>
       </c>
       <c r="F1870" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="H1870" t="s">
         <v>13</v>
@@ -53784,7 +53783,7 @@
         <v>52</v>
       </c>
       <c r="F1871" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="H1871" t="s">
         <v>13</v>
@@ -53804,13 +53803,13 @@
         <v>256</v>
       </c>
       <c r="D1872" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="E1872" t="s">
         <v>31</v>
       </c>
       <c r="F1872" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="H1872" t="s">
         <v>13</v>
@@ -53836,13 +53835,13 @@
         <v>52</v>
       </c>
       <c r="F1873" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="H1873" t="s">
         <v>13</v>
       </c>
       <c r="J1873" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1874" spans="1:10" x14ac:dyDescent="0.35">
@@ -53856,13 +53855,13 @@
         <v>258</v>
       </c>
       <c r="D1874" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="E1874" t="s">
         <v>31</v>
       </c>
       <c r="F1874" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="H1874" t="s">
         <v>13</v>
@@ -53888,13 +53887,13 @@
         <v>52</v>
       </c>
       <c r="F1875" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="H1875" t="s">
         <v>13</v>
       </c>
       <c r="J1875" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1876" spans="1:10" x14ac:dyDescent="0.35">
@@ -53908,13 +53907,13 @@
         <v>260</v>
       </c>
       <c r="D1876" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="E1876" t="s">
         <v>31</v>
       </c>
       <c r="F1876" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="H1876" t="s">
         <v>13</v>
@@ -53934,13 +53933,13 @@
         <v>261</v>
       </c>
       <c r="D1877" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="E1877" t="s">
         <v>31</v>
       </c>
       <c r="F1877" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="H1877" t="s">
         <v>13</v>
@@ -53960,13 +53959,13 @@
         <v>262</v>
       </c>
       <c r="D1878" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="E1878" t="s">
         <v>52</v>
       </c>
       <c r="F1878" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="H1878" t="s">
         <v>13</v>
@@ -54018,7 +54017,7 @@
         <v>767</v>
       </c>
       <c r="F1880" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="H1880" t="s">
         <v>13</v>
@@ -54044,7 +54043,7 @@
         <v>69</v>
       </c>
       <c r="F1881" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="H1881" t="s">
         <v>13</v>
@@ -54064,19 +54063,19 @@
         <v>266</v>
       </c>
       <c r="D1882" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="E1882" t="s">
         <v>31</v>
       </c>
       <c r="F1882" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="H1882" t="s">
         <v>13</v>
       </c>
       <c r="J1882" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1883" spans="1:10" x14ac:dyDescent="0.35">
@@ -54090,13 +54089,13 @@
         <v>267</v>
       </c>
       <c r="D1883" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="E1883" t="s">
         <v>31</v>
       </c>
       <c r="F1883" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="H1883" t="s">
         <v>13</v>
@@ -54116,13 +54115,13 @@
         <v>268</v>
       </c>
       <c r="D1884" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="E1884" t="s">
         <v>31</v>
       </c>
       <c r="F1884" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="H1884" t="s">
         <v>13</v>
@@ -54174,13 +54173,13 @@
         <v>52</v>
       </c>
       <c r="F1886" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="H1886" t="s">
         <v>13</v>
       </c>
       <c r="J1886" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1887" spans="1:10" x14ac:dyDescent="0.35">
@@ -54200,13 +54199,13 @@
         <v>52</v>
       </c>
       <c r="F1887" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="H1887" t="s">
         <v>13</v>
       </c>
       <c r="J1887" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1888" spans="1:10" x14ac:dyDescent="0.35">
@@ -54220,13 +54219,13 @@
         <v>272</v>
       </c>
       <c r="D1888" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="E1888" t="s">
         <v>31</v>
       </c>
       <c r="F1888" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="H1888" t="s">
         <v>13</v>
@@ -54246,13 +54245,13 @@
         <v>273</v>
       </c>
       <c r="D1889" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="E1889" t="s">
         <v>31</v>
       </c>
       <c r="F1889" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="H1889" t="s">
         <v>13</v>
@@ -54278,7 +54277,7 @@
         <v>96</v>
       </c>
       <c r="F1890" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="H1890" t="s">
         <v>13</v>
@@ -54298,13 +54297,13 @@
         <v>275</v>
       </c>
       <c r="D1891" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="E1891" t="s">
         <v>31</v>
       </c>
       <c r="F1891" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="H1891" t="s">
         <v>13</v>
@@ -54324,13 +54323,13 @@
         <v>276</v>
       </c>
       <c r="D1892" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="E1892" t="s">
         <v>31</v>
       </c>
       <c r="F1892" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="H1892" t="s">
         <v>13</v>
@@ -54382,7 +54381,7 @@
         <v>767</v>
       </c>
       <c r="F1894" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="H1894" t="s">
         <v>13</v>
@@ -54408,7 +54407,7 @@
         <v>52</v>
       </c>
       <c r="F1895" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="H1895" t="s">
         <v>13</v>
@@ -54434,13 +54433,13 @@
         <v>31</v>
       </c>
       <c r="F1896" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="H1896" t="s">
         <v>13</v>
       </c>
       <c r="J1896" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1897" spans="1:10" x14ac:dyDescent="0.35">
@@ -54460,13 +54459,13 @@
         <v>52</v>
       </c>
       <c r="F1897" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="H1897" t="s">
         <v>13</v>
       </c>
       <c r="J1897" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1898" spans="1:10" x14ac:dyDescent="0.35">
@@ -54486,7 +54485,7 @@
         <v>31</v>
       </c>
       <c r="F1898" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="H1898" t="s">
         <v>13</v>
@@ -54512,13 +54511,13 @@
         <v>52</v>
       </c>
       <c r="F1899" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H1899" t="s">
         <v>13</v>
       </c>
       <c r="J1899" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1900" spans="1:10" x14ac:dyDescent="0.35">
@@ -54564,7 +54563,7 @@
         <v>52</v>
       </c>
       <c r="F1901" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="H1901" t="s">
         <v>13</v>
@@ -54642,7 +54641,7 @@
         <v>52</v>
       </c>
       <c r="F1904" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="H1904" t="s">
         <v>13</v>
@@ -54662,13 +54661,13 @@
         <v>289</v>
       </c>
       <c r="D1905" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="E1905" t="s">
         <v>31</v>
       </c>
       <c r="F1905" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="H1905" t="s">
         <v>13</v>
@@ -54694,13 +54693,13 @@
         <v>52</v>
       </c>
       <c r="F1906" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="H1906" t="s">
         <v>13</v>
       </c>
       <c r="J1906" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1907" spans="1:10" x14ac:dyDescent="0.35">
@@ -54714,13 +54713,13 @@
         <v>291</v>
       </c>
       <c r="D1907" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="E1907" t="s">
         <v>31</v>
       </c>
       <c r="F1907" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="H1907" t="s">
         <v>13</v>
@@ -54746,7 +54745,7 @@
         <v>52</v>
       </c>
       <c r="F1908" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="H1908" t="s">
         <v>13</v>
@@ -54766,13 +54765,13 @@
         <v>293</v>
       </c>
       <c r="D1909" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="E1909" t="s">
         <v>31</v>
       </c>
       <c r="F1909" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="H1909" t="s">
         <v>13</v>
@@ -54798,7 +54797,7 @@
         <v>52</v>
       </c>
       <c r="F1910" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="H1910" t="s">
         <v>13</v>
@@ -54850,7 +54849,7 @@
         <v>52</v>
       </c>
       <c r="F1912" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="H1912" t="s">
         <v>13</v>
@@ -54876,7 +54875,7 @@
         <v>37</v>
       </c>
       <c r="F1913" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="H1913" t="s">
         <v>13</v>
@@ -54902,7 +54901,7 @@
         <v>52</v>
       </c>
       <c r="F1914" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="H1914" t="s">
         <v>13</v>
@@ -54954,7 +54953,7 @@
         <v>52</v>
       </c>
       <c r="F1916" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="H1916" t="s">
         <v>13</v>
@@ -54980,7 +54979,7 @@
         <v>52</v>
       </c>
       <c r="F1917" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="H1917" t="s">
         <v>13</v>
@@ -55006,13 +55005,13 @@
         <v>52</v>
       </c>
       <c r="F1918" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="H1918" t="s">
         <v>13</v>
       </c>
       <c r="J1918" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1919" spans="1:10" x14ac:dyDescent="0.35">
@@ -55058,7 +55057,7 @@
         <v>767</v>
       </c>
       <c r="F1920" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="H1920" t="s">
         <v>13</v>
@@ -55084,7 +55083,7 @@
         <v>196</v>
       </c>
       <c r="F1921" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="H1921" t="s">
         <v>13</v>
@@ -55136,7 +55135,7 @@
         <v>196</v>
       </c>
       <c r="F1923" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="H1923" t="s">
         <v>13</v>
@@ -55162,7 +55161,7 @@
         <v>196</v>
       </c>
       <c r="F1924" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="H1924" t="s">
         <v>13</v>
@@ -55188,7 +55187,7 @@
         <v>196</v>
       </c>
       <c r="F1925" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="H1925" t="s">
         <v>13</v>
@@ -55214,7 +55213,7 @@
         <v>196</v>
       </c>
       <c r="F1926" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="H1926" t="s">
         <v>13</v>
@@ -55240,7 +55239,7 @@
         <v>196</v>
       </c>
       <c r="F1927" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="H1927" t="s">
         <v>13</v>
@@ -55266,7 +55265,7 @@
         <v>196</v>
       </c>
       <c r="F1928" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="H1928" t="s">
         <v>13</v>
@@ -55318,7 +55317,7 @@
         <v>767</v>
       </c>
       <c r="F1930" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="H1930" t="s">
         <v>13</v>
@@ -55344,7 +55343,7 @@
         <v>767</v>
       </c>
       <c r="F1931" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="H1931" t="s">
         <v>13</v>
@@ -55370,7 +55369,7 @@
         <v>31</v>
       </c>
       <c r="F1932" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="H1932" t="s">
         <v>13</v>
@@ -55396,7 +55395,7 @@
         <v>31</v>
       </c>
       <c r="F1933" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="H1933" t="s">
         <v>13</v>
@@ -55448,7 +55447,7 @@
         <v>31</v>
       </c>
       <c r="F1935" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="H1935" t="s">
         <v>13</v>
@@ -55474,7 +55473,7 @@
         <v>31</v>
       </c>
       <c r="F1936" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="H1936" t="s">
         <v>13</v>
@@ -55500,7 +55499,7 @@
         <v>52</v>
       </c>
       <c r="F1937" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="H1937" t="s">
         <v>13</v>
@@ -55526,7 +55525,7 @@
         <v>31</v>
       </c>
       <c r="F1938" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="H1938" t="s">
         <v>13</v>
@@ -55578,7 +55577,7 @@
         <v>31</v>
       </c>
       <c r="F1940" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="H1940" t="s">
         <v>13</v>
@@ -55682,7 +55681,7 @@
         <v>31</v>
       </c>
       <c r="F1944" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="H1944" t="s">
         <v>13</v>
@@ -55708,7 +55707,7 @@
         <v>31</v>
       </c>
       <c r="F1945" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="H1945" t="s">
         <v>13</v>
@@ -55760,7 +55759,7 @@
         <v>31</v>
       </c>
       <c r="F1947" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="H1947" t="s">
         <v>13</v>
@@ -55812,7 +55811,7 @@
         <v>31</v>
       </c>
       <c r="F1949" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="H1949" t="s">
         <v>13</v>
@@ -55864,7 +55863,7 @@
         <v>31</v>
       </c>
       <c r="F1951" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="H1951" t="s">
         <v>13</v>
@@ -55890,7 +55889,7 @@
         <v>31</v>
       </c>
       <c r="F1952" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="H1952" t="s">
         <v>13</v>
@@ -55968,7 +55967,7 @@
         <v>31</v>
       </c>
       <c r="F1955" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="H1955" t="s">
         <v>13</v>
@@ -55994,7 +55993,7 @@
         <v>69</v>
       </c>
       <c r="F1956" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="H1956" t="s">
         <v>13</v>
@@ -56020,7 +56019,7 @@
         <v>31</v>
       </c>
       <c r="F1957" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="H1957" t="s">
         <v>13</v>
@@ -56046,7 +56045,7 @@
         <v>31</v>
       </c>
       <c r="F1958" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="H1958" t="s">
         <v>13</v>
@@ -56072,7 +56071,7 @@
         <v>31</v>
       </c>
       <c r="F1959" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="H1959" t="s">
         <v>13</v>
@@ -56098,7 +56097,7 @@
         <v>69</v>
       </c>
       <c r="F1960" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="H1960" t="s">
         <v>13</v>
@@ -56124,7 +56123,7 @@
         <v>31</v>
       </c>
       <c r="F1961" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="H1961" t="s">
         <v>13</v>
@@ -56202,7 +56201,7 @@
         <v>31</v>
       </c>
       <c r="F1964" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="H1964" t="s">
         <v>13</v>
@@ -56228,13 +56227,13 @@
         <v>69</v>
       </c>
       <c r="F1965" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="H1965" t="s">
         <v>13</v>
       </c>
       <c r="J1965" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1966" spans="1:10" x14ac:dyDescent="0.35">
@@ -56254,7 +56253,7 @@
         <v>31</v>
       </c>
       <c r="F1966" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="H1966" t="s">
         <v>13</v>
@@ -56280,7 +56279,7 @@
         <v>31</v>
       </c>
       <c r="F1967" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="H1967" t="s">
         <v>13</v>
@@ -56306,13 +56305,13 @@
         <v>96</v>
       </c>
       <c r="F1968" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="H1968" t="s">
         <v>13</v>
       </c>
       <c r="J1968" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1969" spans="1:10" x14ac:dyDescent="0.35">
@@ -56332,7 +56331,7 @@
         <v>31</v>
       </c>
       <c r="F1969" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="H1969" t="s">
         <v>13</v>
@@ -56358,7 +56357,7 @@
         <v>31</v>
       </c>
       <c r="G1970" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="H1970" t="s">
         <v>17</v>
@@ -56384,7 +56383,7 @@
         <v>37</v>
       </c>
       <c r="G1971" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="H1971" t="s">
         <v>17</v>
@@ -56410,7 +56409,7 @@
         <v>767</v>
       </c>
       <c r="F1972" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="H1972" t="s">
         <v>13</v>
@@ -56436,7 +56435,7 @@
         <v>31</v>
       </c>
       <c r="F1973" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="H1973" t="s">
         <v>13</v>
@@ -56462,7 +56461,7 @@
         <v>767</v>
       </c>
       <c r="F1974" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="H1974" t="s">
         <v>13</v>
@@ -56488,7 +56487,7 @@
         <v>69</v>
       </c>
       <c r="F1975" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="H1975" t="s">
         <v>13</v>
@@ -56540,13 +56539,13 @@
         <v>69</v>
       </c>
       <c r="F1977" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="H1977" t="s">
         <v>13</v>
       </c>
       <c r="J1977" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1978" spans="1:10" x14ac:dyDescent="0.35">
@@ -56592,7 +56591,7 @@
         <v>767</v>
       </c>
       <c r="F1979" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="H1979" t="s">
         <v>13</v>
@@ -56618,13 +56617,13 @@
         <v>52</v>
       </c>
       <c r="F1980" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="H1980" t="s">
         <v>13</v>
       </c>
       <c r="J1980" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1981" spans="1:10" x14ac:dyDescent="0.35">
@@ -56644,7 +56643,7 @@
         <v>52</v>
       </c>
       <c r="G1981" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="H1981" t="s">
         <v>17</v>
@@ -56670,7 +56669,7 @@
         <v>166</v>
       </c>
       <c r="G1982" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="H1982" t="s">
         <v>17</v>
@@ -56696,7 +56695,7 @@
         <v>767</v>
       </c>
       <c r="F1983" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="H1983" t="s">
         <v>13</v>
@@ -56722,7 +56721,7 @@
         <v>166</v>
       </c>
       <c r="F1984" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="H1984" t="s">
         <v>13</v>
@@ -56800,7 +56799,7 @@
         <v>166</v>
       </c>
       <c r="F1987" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="H1987" t="s">
         <v>13</v>
@@ -56852,7 +56851,7 @@
         <v>166</v>
       </c>
       <c r="F1989" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="H1989" t="s">
         <v>13</v>
@@ -56878,7 +56877,7 @@
         <v>166</v>
       </c>
       <c r="F1990" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="H1990" t="s">
         <v>13</v>
@@ -56930,7 +56929,7 @@
         <v>69</v>
       </c>
       <c r="F1992" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="H1992" t="s">
         <v>13</v>
@@ -56956,7 +56955,7 @@
         <v>767</v>
       </c>
       <c r="F1993" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H1993" t="s">
         <v>13</v>
@@ -56982,7 +56981,7 @@
         <v>767</v>
       </c>
       <c r="F1994" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="H1994" t="s">
         <v>13</v>
@@ -57005,7 +57004,7 @@
         <v>1202</v>
       </c>
       <c r="H1995" t="s">
-        <v>1563</v>
+        <v>17</v>
       </c>
       <c r="I1995" t="s">
         <v>18</v>
@@ -57450,7 +57449,7 @@
         <v>13</v>
       </c>
       <c r="J2012" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2013" spans="1:10" x14ac:dyDescent="0.35">
@@ -57782,7 +57781,7 @@
         <v>37</v>
       </c>
       <c r="F2025" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="H2025" t="s">
         <v>13</v>
